--- a/BVSimulationFiles/36.xlsx
+++ b/BVSimulationFiles/36.xlsx
@@ -6,11 +6,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet1 Copy" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet1 Copy" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1 Copy Copy" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -414,75 +414,63 @@
         <v>0</v>
       </c>
       <c r="C1" t="n">
-        <v>0.001579166666666667</v>
+        <v>0.001895</v>
       </c>
       <c r="D1" t="n">
-        <v>0.003158333333333334</v>
+        <v>0.00379</v>
       </c>
       <c r="E1" t="n">
-        <v>0.0047375</v>
+        <v>0.005685000000000001</v>
       </c>
       <c r="F1" t="n">
-        <v>0.006316666666666667</v>
+        <v>0.007580000000000001</v>
       </c>
       <c r="G1" t="n">
-        <v>0.007895833333333335</v>
+        <v>0.009475000000000001</v>
       </c>
       <c r="H1" t="n">
-        <v>0.009475000000000001</v>
+        <v>0.01137</v>
       </c>
       <c r="I1" t="n">
-        <v>0.01105416666666667</v>
+        <v>0.013265</v>
       </c>
       <c r="J1" t="n">
-        <v>0.01263333333333333</v>
+        <v>0.01516</v>
       </c>
       <c r="K1" t="n">
-        <v>0.0142125</v>
+        <v>0.017055</v>
       </c>
       <c r="L1" t="n">
-        <v>0.01579166666666667</v>
+        <v>0.01895</v>
       </c>
       <c r="M1" t="n">
-        <v>0.01737083333333334</v>
+        <v>0.020845</v>
       </c>
       <c r="N1" t="n">
-        <v>0.01895</v>
+        <v>0.02274</v>
       </c>
       <c r="O1" t="n">
-        <v>0.02052916666666667</v>
+        <v>0.024635</v>
       </c>
       <c r="P1" t="n">
-        <v>0.02210833333333334</v>
+        <v>0.02653</v>
       </c>
       <c r="Q1" t="n">
-        <v>0.0236875</v>
+        <v>0.028425</v>
       </c>
       <c r="R1" t="n">
-        <v>0.02526666666666667</v>
+        <v>0.03032</v>
       </c>
       <c r="S1" t="n">
-        <v>0.02684583333333334</v>
+        <v>0.032215</v>
       </c>
       <c r="T1" t="n">
-        <v>0.028425</v>
+        <v>0.03411</v>
       </c>
       <c r="U1" t="n">
-        <v>0.03000416666666667</v>
+        <v>0.036005</v>
       </c>
       <c r="V1" t="n">
-        <v>0.03158333333333334</v>
-      </c>
-      <c r="W1" t="n">
-        <v>0.0331625</v>
-      </c>
-      <c r="X1" t="n">
-        <v>0.03474166666666667</v>
-      </c>
-      <c r="Y1" t="n">
-        <v>0.03632083333333334</v>
-      </c>
-      <c r="Z1" t="n">
         <v>0.0379</v>
       </c>
     </row>
